--- a/Summary.xlsx
+++ b/Summary.xlsx
@@ -528,7 +528,7 @@
       <c r="U1" s="1" t="n"/>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>LMA g/m2</t>
+          <t>Specific leaf area (cm²/g)</t>
         </is>
       </c>
       <c r="W1" s="1" t="n"/>
@@ -722,10 +722,10 @@
         <v>2.92</v>
       </c>
       <c r="V4" t="n">
-        <v>109.65</v>
+        <v>92.05</v>
       </c>
       <c r="W4" t="n">
-        <v>12.98</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="5">
@@ -773,7 +773,7 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>89.23999999999999</v>
+        <v>112.06</v>
       </c>
       <c r="W5" t="inlineStr"/>
     </row>
@@ -840,10 +840,10 @@
         <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>92.81</v>
+        <v>108.27</v>
       </c>
       <c r="W6" t="n">
-        <v>7.27</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -909,10 +909,10 @@
         <v>3.13</v>
       </c>
       <c r="V7" t="n">
-        <v>104.87</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>6.63</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="8">
@@ -982,10 +982,10 @@
         <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>124.79</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>13.53</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="9">
@@ -1051,10 +1051,10 @@
         <v>2.54</v>
       </c>
       <c r="V9" t="n">
-        <v>130.76</v>
+        <v>78.87</v>
       </c>
       <c r="W9" t="n">
-        <v>23.72</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="10">
@@ -1120,10 +1120,10 @@
         <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>124.93</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>13.88</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="11">
@@ -1189,10 +1189,10 @@
         <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>130.47</v>
+        <v>78.02</v>
       </c>
       <c r="W11" t="n">
-        <v>19.67</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="12">
@@ -1264,10 +1264,10 @@
         <v>6.87</v>
       </c>
       <c r="V12" t="n">
-        <v>283.91</v>
+        <v>35.67</v>
       </c>
       <c r="W12" t="n">
-        <v>33.02</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="13">
@@ -1333,10 +1333,10 @@
         <v>4.76</v>
       </c>
       <c r="V13" t="n">
-        <v>272.72</v>
+        <v>36.94</v>
       </c>
       <c r="W13" t="n">
-        <v>24.68</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="14">
@@ -1402,10 +1402,10 @@
         <v>4.66</v>
       </c>
       <c r="V14" t="n">
-        <v>292.24</v>
+        <v>34.5</v>
       </c>
       <c r="W14" t="n">
-        <v>28.66</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="15">
@@ -1471,10 +1471,10 @@
         <v>4.67</v>
       </c>
       <c r="V15" t="n">
-        <v>282.56</v>
+        <v>35.98</v>
       </c>
       <c r="W15" t="n">
-        <v>38.74</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="16">
@@ -1544,10 +1544,10 @@
         <v>6.88</v>
       </c>
       <c r="V16" t="n">
-        <v>279.18</v>
+        <v>36.24</v>
       </c>
       <c r="W16" t="n">
-        <v>29.99</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="17">
@@ -1613,10 +1613,10 @@
         <v>4.13</v>
       </c>
       <c r="V17" t="n">
-        <v>283.62</v>
+        <v>35.42</v>
       </c>
       <c r="W17" t="n">
-        <v>21.17</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="18">
@@ -1682,10 +1682,10 @@
         <v>3.86</v>
       </c>
       <c r="V18" t="n">
-        <v>277.49</v>
+        <v>36.19</v>
       </c>
       <c r="W18" t="n">
-        <v>19.23</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="19">
@@ -1751,10 +1751,10 @@
         <v>6.25</v>
       </c>
       <c r="V19" t="n">
-        <v>294.01</v>
+        <v>34.37</v>
       </c>
       <c r="W19" t="n">
-        <v>34.93</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -1826,10 +1826,10 @@
         <v>2.77</v>
       </c>
       <c r="V20" t="n">
-        <v>151.75</v>
+        <v>68.88</v>
       </c>
       <c r="W20" t="n">
-        <v>36.15</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="21">
@@ -1895,10 +1895,10 @@
         <v>4.81</v>
       </c>
       <c r="V21" t="n">
-        <v>163.15</v>
+        <v>61.86</v>
       </c>
       <c r="W21" t="n">
-        <v>16.45</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="22">
@@ -1964,10 +1964,10 @@
         <v>2.81</v>
       </c>
       <c r="V22" t="n">
-        <v>152.19</v>
+        <v>65.98</v>
       </c>
       <c r="W22" t="n">
-        <v>12.12</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="23">
@@ -2033,10 +2033,10 @@
         <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>132.7</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>23.55</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="24">
@@ -2106,10 +2106,10 @@
         <v>5.79</v>
       </c>
       <c r="V24" t="n">
-        <v>143.54</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>13.32</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="25">
@@ -2175,10 +2175,10 @@
         <v>5.23</v>
       </c>
       <c r="V25" t="n">
-        <v>145.96</v>
+        <v>69.55</v>
       </c>
       <c r="W25" t="n">
-        <v>19.85</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2244,10 +2244,10 @@
         <v>0.31</v>
       </c>
       <c r="V26" t="n">
-        <v>139.03</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>12.31</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="27">
@@ -2313,10 +2313,10 @@
         <v>5.19</v>
       </c>
       <c r="V27" t="n">
-        <v>138.13</v>
+        <v>72.58</v>
       </c>
       <c r="W27" t="n">
-        <v>7.51</v>
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>
